--- a/bao-cao-doanh-thu/thông tin khách hàng đặt hàng.xlsx
+++ b/bao-cao-doanh-thu/thông tin khách hàng đặt hàng.xlsx
@@ -621,7 +621,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <f>IFERROR(QUERY({IMPORTRANGE($B$3,"'Tháng 6'!B8:N407");IMPORTRANGE($B$3,"'Tháng 7'!B8:N407");IMPORTRANGE($B$3,"'Tháng 8'!B8:N407");IMPORTRANGE($B$3,"'Tháng 9'!B8:N407");IMPORTRANGE($B$3,"'Tháng 10'!B8:N407");IMPORTRANGE($B$3,"'Tháng 11'!B8:N407");IMPORTRANGE($B$3,"'Tháng 12'!B8:N407")},"select Col1,Col2,Col5,Col12,Col3,Col6,Col9,Col11 where Col1 is not null order by Col1",0),"⚠ Chưa kết nối: bấm vào ô màu vàng ở dòng 3 rồi bấm nút Cho phép truy cập (Allow access)")</f>
+        <f>IFERROR(QUERY({IMPORTRANGE($B$3,"'Tháng 6'!B10:N89");IMPORTRANGE($B$3,"'Tháng 6'!B92:N171");IMPORTRANGE($B$3,"'Tháng 6'!B174:N253");IMPORTRANGE($B$3,"'Tháng 6'!B256:N335");IMPORTRANGE($B$3,"'Tháng 7'!B10:N89");IMPORTRANGE($B$3,"'Tháng 7'!B92:N171");IMPORTRANGE($B$3,"'Tháng 7'!B174:N253");IMPORTRANGE($B$3,"'Tháng 7'!B256:N335");IMPORTRANGE($B$3,"'Tháng 8'!B10:N89");IMPORTRANGE($B$3,"'Tháng 8'!B92:N171");IMPORTRANGE($B$3,"'Tháng 8'!B174:N253");IMPORTRANGE($B$3,"'Tháng 8'!B256:N335");IMPORTRANGE($B$3,"'Tháng 9'!B10:N89");IMPORTRANGE($B$3,"'Tháng 9'!B92:N171");IMPORTRANGE($B$3,"'Tháng 9'!B174:N253");IMPORTRANGE($B$3,"'Tháng 9'!B256:N335");IMPORTRANGE($B$3,"'Tháng 10'!B10:N89");IMPORTRANGE($B$3,"'Tháng 10'!B92:N171");IMPORTRANGE($B$3,"'Tháng 10'!B174:N253");IMPORTRANGE($B$3,"'Tháng 10'!B256:N335");IMPORTRANGE($B$3,"'Tháng 11'!B10:N89");IMPORTRANGE($B$3,"'Tháng 11'!B92:N171");IMPORTRANGE($B$3,"'Tháng 11'!B174:N253");IMPORTRANGE($B$3,"'Tháng 11'!B256:N335");IMPORTRANGE($B$3,"'Tháng 12'!B10:N89");IMPORTRANGE($B$3,"'Tháng 12'!B92:N171");IMPORTRANGE($B$3,"'Tháng 12'!B174:N253");IMPORTRANGE($B$3,"'Tháng 12'!B256:N335")},"select Col1,Col2,Col5,Col12,Col3,Col6,Col9,Col11 where Col1 is not null order by Col1",0),"⚠ Chưa kết nối: bấm vào ô màu vàng ở dòng 3 rồi bấm nút Cho phép truy cập (Allow access)")</f>
         <v/>
       </c>
     </row>
